--- a/maliye/2024/2024-05-29 Usulsuzluk-ceza/ceza bedelleri.xlsx
+++ b/maliye/2024/2024-05-29 Usulsuzluk-ceza/ceza bedelleri.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\maliye\2024\2024-05-29 Usulsuzluk-ceza\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\comprg\aagitme\yzhn\maliye\2024\2024-05-29 Usulsuzluk-ceza\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACB95E9-C8B8-41E9-82CA-366DCB20DF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A18F244-D40A-4B10-B15C-EBBA74A03BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10620" yWindow="2055" windowWidth="18540" windowHeight="12270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -366,13 +357,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:D10"/>
+  <dimension ref="B3:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -382,8 +373,11 @@
       <c r="D3">
         <v>3700</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -393,8 +387,11 @@
       <c r="D4">
         <v>2500</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -404,8 +401,11 @@
       <c r="D5">
         <v>7300</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -415,8 +415,11 @@
       <c r="D6">
         <v>8500</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -426,8 +429,11 @@
       <c r="D7">
         <v>3000</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>4</v>
       </c>
@@ -437,8 +443,11 @@
       <c r="D8">
         <v>4300</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D10">
         <f>SUM(D3:D9)</f>
         <v>29300</v>
